--- a/Data_Ecoli/P2_2.xlsx
+++ b/Data_Ecoli/P2_2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Degas_Experiment\Data_Ecoli\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\Degas_experiment\Data_Ecoli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{151A1D5F-2355-4D7E-9523-6F17F844F464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D55D8EE-6BA9-4FB2-A042-8E750FC2A690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="10">
   <si>
     <t>Group</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -59,15 +59,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>75_unstirred_2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>75_unstirred_1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>75_unstirred_3</t>
+    <t>75_unstirred_2</t>
   </si>
 </sst>
 </file>
@@ -393,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="10.77734375" customWidth="1"/>
@@ -424,7 +420,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>20</v>
@@ -447,7 +443,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3">
         <v>19</v>
@@ -470,7 +466,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4">
         <v>18</v>
@@ -493,7 +489,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5">
         <v>17</v>
@@ -516,7 +512,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>16</v>
@@ -539,7 +535,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7">
         <v>15</v>
@@ -562,7 +558,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8">
         <v>14</v>
@@ -585,7 +581,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9">
         <v>13</v>
@@ -608,7 +604,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10">
         <v>12</v>
@@ -631,7 +627,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11">
         <v>11</v>
@@ -654,7 +650,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12">
         <v>10</v>
@@ -677,7 +673,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B13">
         <v>9</v>
@@ -700,7 +696,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14">
         <v>8</v>
@@ -723,7 +719,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15">
         <v>7</v>
@@ -746,7 +742,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B16">
         <v>6</v>
@@ -769,7 +765,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -792,7 +788,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18">
         <v>4</v>
@@ -815,7 +811,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B19">
         <v>3</v>
@@ -838,7 +834,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -861,7 +857,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -1317,897 +1313,437 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42">
-        <v>26.204999999999998</v>
+        <v>21.655999999999999</v>
       </c>
       <c r="D42">
-        <v>0.58199999999999996</v>
+        <v>0.54800000000000004</v>
       </c>
       <c r="E42">
-        <v>0.13500000000000001</v>
+        <v>0.113</v>
       </c>
       <c r="F42">
-        <v>84.9</v>
+        <v>206.4</v>
       </c>
       <c r="G42" s="1">
-        <v>26532.39</v>
+        <v>47261.18</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B43">
         <v>2</v>
       </c>
       <c r="C43">
-        <v>25.619</v>
+        <v>21.809000000000001</v>
       </c>
       <c r="D43">
-        <v>0.65400000000000003</v>
+        <v>0.43099999999999999</v>
       </c>
       <c r="E43">
-        <v>0.14899999999999999</v>
-      </c>
-      <c r="F43">
-        <v>60.8</v>
+        <v>0.15</v>
       </c>
       <c r="G43" s="1">
-        <v>31829.49</v>
+        <v>35565.760000000002</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B44">
         <v>3</v>
       </c>
       <c r="C44">
-        <v>26.298999999999999</v>
+        <v>21.411000000000001</v>
       </c>
       <c r="D44">
-        <v>0.432</v>
+        <v>0.40100000000000002</v>
       </c>
       <c r="E44">
-        <v>0.156</v>
-      </c>
-      <c r="F44">
-        <v>52.1</v>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="G44" s="1">
-        <v>28302.73</v>
+        <v>51838.06</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B45">
         <v>4</v>
       </c>
       <c r="C45">
-        <v>26.51</v>
+        <v>21.39</v>
       </c>
       <c r="D45">
-        <v>0.432</v>
+        <v>0.51400000000000001</v>
       </c>
       <c r="E45">
-        <v>0.188</v>
+        <v>0.17399999999999999</v>
       </c>
       <c r="F45">
-        <v>29.5</v>
+        <v>376.7</v>
       </c>
       <c r="G45" s="1">
-        <v>15005.7</v>
+        <v>79222.12</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B46">
         <v>5</v>
       </c>
       <c r="C46">
-        <v>26.483000000000001</v>
+        <v>21.588999999999999</v>
       </c>
       <c r="D46">
-        <v>0.73</v>
+        <v>0.41599999999999998</v>
       </c>
       <c r="E46">
-        <v>0.14199999999999999</v>
-      </c>
-      <c r="F46">
-        <v>82.4</v>
+        <v>0.187</v>
       </c>
       <c r="G46" s="1">
-        <v>56831.72</v>
+        <v>120239.53</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B47">
         <v>6</v>
       </c>
       <c r="C47">
-        <v>29.366</v>
+        <v>21.279</v>
       </c>
       <c r="D47">
-        <v>0.89800000000000002</v>
+        <v>0.48</v>
       </c>
       <c r="E47">
-        <v>0.19500000000000001</v>
-      </c>
-      <c r="F47">
-        <v>80.8</v>
+        <v>0.191</v>
       </c>
       <c r="G47" s="1">
-        <v>36083</v>
+        <v>50665.41</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B48">
         <v>7</v>
       </c>
       <c r="C48">
-        <v>26.372</v>
+        <v>21.631</v>
       </c>
       <c r="D48">
-        <v>0.52600000000000002</v>
+        <v>0.48199999999999998</v>
       </c>
       <c r="E48">
-        <v>0.121</v>
-      </c>
-      <c r="F48">
-        <v>34.1</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="G48" s="1">
-        <v>24898.98</v>
+        <v>89129.63</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B49">
         <v>8</v>
       </c>
       <c r="C49">
-        <v>27.597000000000001</v>
+        <v>21.544</v>
       </c>
       <c r="D49">
-        <v>0.499</v>
+        <v>0.39900000000000002</v>
       </c>
       <c r="E49">
-        <v>0.161</v>
-      </c>
-      <c r="F49">
-        <v>46.7</v>
+        <v>0.10199999999999999</v>
       </c>
       <c r="G49" s="1">
-        <v>23452.880000000001</v>
+        <v>116167.28</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B50">
         <v>9</v>
       </c>
       <c r="C50">
-        <v>27.035</v>
+        <v>21.584</v>
       </c>
       <c r="D50">
-        <v>0.63200000000000001</v>
+        <v>0.36499999999999999</v>
       </c>
       <c r="E50">
-        <v>0.152</v>
-      </c>
-      <c r="F50">
-        <v>70.2</v>
+        <v>0.153</v>
       </c>
       <c r="G50" s="1">
-        <v>41588.49</v>
+        <v>100462.86</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B51">
         <v>10</v>
       </c>
       <c r="C51">
-        <v>27.021000000000001</v>
+        <v>21.577999999999999</v>
       </c>
       <c r="D51">
-        <v>0.625</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="E51">
-        <v>0.14799999999999999</v>
-      </c>
-      <c r="F51">
-        <v>78.2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="G51" s="1">
-        <v>45240.68</v>
+        <v>49902.31</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B52">
         <v>11</v>
       </c>
       <c r="C52">
-        <v>28.585000000000001</v>
+        <v>21.6</v>
       </c>
       <c r="D52">
-        <v>0.63200000000000001</v>
+        <v>0.61499999999999999</v>
       </c>
       <c r="E52">
-        <v>0.14099999999999999</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="F52">
-        <v>112.7</v>
+        <v>347.1</v>
       </c>
       <c r="G52" s="1">
-        <v>41990.31</v>
+        <v>74663.62</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B53">
         <v>12</v>
       </c>
       <c r="C53">
-        <v>28.776</v>
+        <v>21.661000000000001</v>
       </c>
       <c r="D53">
-        <v>0.749</v>
+        <v>0.51600000000000001</v>
       </c>
       <c r="E53">
-        <v>0.153</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="F53">
-        <v>118.3</v>
+        <v>162.9</v>
       </c>
       <c r="G53" s="1">
-        <v>51693.2</v>
+        <v>39054.39</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B54">
         <v>13</v>
       </c>
       <c r="C54">
-        <v>29.896999999999998</v>
+        <v>21.498000000000001</v>
       </c>
       <c r="D54">
-        <v>0.432</v>
+        <v>0.46400000000000002</v>
       </c>
       <c r="E54">
-        <v>0.20399999999999999</v>
+        <v>0.182</v>
       </c>
       <c r="F54">
-        <v>38.299999999999997</v>
+        <v>174.3</v>
       </c>
       <c r="G54" s="1">
-        <v>18962.04</v>
+        <v>45155.85</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B55">
         <v>14</v>
       </c>
       <c r="C55">
-        <v>28.896000000000001</v>
+        <v>21.513999999999999</v>
       </c>
       <c r="D55">
-        <v>0.41599999999999998</v>
+        <v>0.39900000000000002</v>
       </c>
       <c r="E55">
-        <v>0.187</v>
+        <v>0.114</v>
       </c>
       <c r="F55">
-        <v>59.6</v>
+        <v>225.3</v>
       </c>
       <c r="G55" s="1">
-        <v>23363.3</v>
+        <v>60261.94</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B56">
         <v>15</v>
       </c>
       <c r="C56">
-        <v>30.649000000000001</v>
+        <v>21.965</v>
       </c>
       <c r="D56">
-        <v>0.54900000000000004</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="E56">
-        <v>0.17</v>
+        <v>0.184</v>
       </c>
       <c r="F56">
-        <v>97.2</v>
+        <v>87.6</v>
       </c>
       <c r="G56" s="1">
-        <v>52439.78</v>
+        <v>38752.36</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B57">
         <v>16</v>
       </c>
       <c r="C57">
-        <v>30.843</v>
+        <v>21.831</v>
       </c>
       <c r="D57">
-        <v>0.432</v>
+        <v>0.51400000000000001</v>
       </c>
       <c r="E57">
-        <v>0.16700000000000001</v>
+        <v>0.13800000000000001</v>
       </c>
       <c r="F57">
-        <v>105.7</v>
+        <v>275.8</v>
       </c>
       <c r="G57" s="1">
-        <v>48420.480000000003</v>
+        <v>76670.5</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B58">
         <v>17</v>
       </c>
       <c r="C58">
-        <v>30.73</v>
+        <v>22.347000000000001</v>
       </c>
       <c r="D58">
-        <v>0.71499999999999997</v>
+        <v>0.54</v>
       </c>
       <c r="E58">
-        <v>0.17199999999999999</v>
+        <v>0.19800000000000001</v>
       </c>
       <c r="F58">
-        <v>135</v>
+        <v>263.7</v>
       </c>
       <c r="G58" s="1">
-        <v>49782.239999999998</v>
+        <v>67500.7</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B59">
         <v>18</v>
       </c>
       <c r="C59">
-        <v>32.052</v>
+        <v>22.491</v>
       </c>
       <c r="D59">
-        <v>0.76100000000000001</v>
+        <v>0.51400000000000001</v>
       </c>
       <c r="E59">
-        <v>0.19800000000000001</v>
+        <v>0.161</v>
       </c>
       <c r="F59">
-        <v>160.30000000000001</v>
+        <v>216.9</v>
       </c>
       <c r="G59" s="1">
-        <v>41108.31</v>
+        <v>59772.29</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B60">
         <v>19</v>
       </c>
       <c r="C60">
-        <v>32.204000000000001</v>
+        <v>22.45</v>
       </c>
       <c r="D60">
-        <v>0.76400000000000001</v>
+        <v>0.496</v>
       </c>
       <c r="E60">
-        <v>0.20399999999999999</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="F60">
-        <v>149.1</v>
+        <v>174.8</v>
       </c>
       <c r="G60" s="1">
-        <v>41213.199999999997</v>
+        <v>79004.039999999994</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B61">
         <v>20</v>
       </c>
       <c r="C61">
-        <v>33.741</v>
+        <v>22.472000000000001</v>
       </c>
       <c r="D61">
-        <v>0.86</v>
+        <v>0.46600000000000003</v>
       </c>
       <c r="E61">
-        <v>0.26500000000000001</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="F61">
-        <v>93.9</v>
+        <v>0.17100000000000001</v>
       </c>
       <c r="G61" s="1">
-        <v>36747.03</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>10</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
-      </c>
-      <c r="C62">
-        <v>21.655999999999999</v>
-      </c>
-      <c r="D62">
-        <v>0.54800000000000004</v>
-      </c>
-      <c r="E62">
-        <v>0.113</v>
-      </c>
-      <c r="F62">
-        <v>206.4</v>
-      </c>
-      <c r="G62" s="1">
-        <v>47261.18</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>10</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
-      </c>
-      <c r="C63">
-        <v>21.809000000000001</v>
-      </c>
-      <c r="D63">
-        <v>0.43099999999999999</v>
-      </c>
-      <c r="E63">
-        <v>0.15</v>
-      </c>
-      <c r="G63" s="1">
-        <v>35565.760000000002</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>10</v>
-      </c>
-      <c r="B64">
-        <v>3</v>
-      </c>
-      <c r="C64">
-        <v>21.411000000000001</v>
-      </c>
-      <c r="D64">
-        <v>0.40100000000000002</v>
-      </c>
-      <c r="E64">
-        <v>9.2999999999999999E-2</v>
-      </c>
-      <c r="G64" s="1">
-        <v>51838.06</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>10</v>
-      </c>
-      <c r="B65">
-        <v>4</v>
-      </c>
-      <c r="C65">
-        <v>21.39</v>
-      </c>
-      <c r="D65">
-        <v>0.51400000000000001</v>
-      </c>
-      <c r="E65">
-        <v>0.17399999999999999</v>
-      </c>
-      <c r="F65">
-        <v>376.7</v>
-      </c>
-      <c r="G65" s="1">
-        <v>79222.12</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>10</v>
-      </c>
-      <c r="B66">
-        <v>5</v>
-      </c>
-      <c r="C66">
-        <v>21.588999999999999</v>
-      </c>
-      <c r="D66">
-        <v>0.41599999999999998</v>
-      </c>
-      <c r="E66">
-        <v>0.187</v>
-      </c>
-      <c r="G66" s="1">
-        <v>120239.53</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>10</v>
-      </c>
-      <c r="B67">
-        <v>6</v>
-      </c>
-      <c r="C67">
-        <v>21.279</v>
-      </c>
-      <c r="D67">
-        <v>0.48</v>
-      </c>
-      <c r="E67">
-        <v>0.191</v>
-      </c>
-      <c r="G67" s="1">
-        <v>50665.41</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>10</v>
-      </c>
-      <c r="B68">
-        <v>7</v>
-      </c>
-      <c r="C68">
-        <v>21.631</v>
-      </c>
-      <c r="D68">
-        <v>0.48199999999999998</v>
-      </c>
-      <c r="E68">
-        <v>0.14599999999999999</v>
-      </c>
-      <c r="G68" s="1">
-        <v>89129.63</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>10</v>
-      </c>
-      <c r="B69">
-        <v>8</v>
-      </c>
-      <c r="C69">
-        <v>21.544</v>
-      </c>
-      <c r="D69">
-        <v>0.39900000000000002</v>
-      </c>
-      <c r="E69">
-        <v>0.10199999999999999</v>
-      </c>
-      <c r="G69" s="1">
-        <v>116167.28</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>10</v>
-      </c>
-      <c r="B70">
-        <v>9</v>
-      </c>
-      <c r="C70">
-        <v>21.584</v>
-      </c>
-      <c r="D70">
-        <v>0.36499999999999999</v>
-      </c>
-      <c r="E70">
-        <v>0.153</v>
-      </c>
-      <c r="G70" s="1">
-        <v>100462.86</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>10</v>
-      </c>
-      <c r="B71">
-        <v>10</v>
-      </c>
-      <c r="C71">
-        <v>21.577999999999999</v>
-      </c>
-      <c r="D71">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="E71">
-        <v>5.5E-2</v>
-      </c>
-      <c r="G71" s="1">
-        <v>49902.31</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>10</v>
-      </c>
-      <c r="B72">
-        <v>11</v>
-      </c>
-      <c r="C72">
-        <v>21.6</v>
-      </c>
-      <c r="D72">
-        <v>0.61499999999999999</v>
-      </c>
-      <c r="E72">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="F72">
-        <v>347.1</v>
-      </c>
-      <c r="G72" s="1">
-        <v>74663.62</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>10</v>
-      </c>
-      <c r="B73">
-        <v>12</v>
-      </c>
-      <c r="C73">
-        <v>21.661000000000001</v>
-      </c>
-      <c r="D73">
-        <v>0.51600000000000001</v>
-      </c>
-      <c r="E73">
-        <v>0.20200000000000001</v>
-      </c>
-      <c r="F73">
-        <v>162.9</v>
-      </c>
-      <c r="G73" s="1">
-        <v>39054.39</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>10</v>
-      </c>
-      <c r="B74">
-        <v>13</v>
-      </c>
-      <c r="C74">
-        <v>21.498000000000001</v>
-      </c>
-      <c r="D74">
-        <v>0.46400000000000002</v>
-      </c>
-      <c r="E74">
-        <v>0.182</v>
-      </c>
-      <c r="F74">
-        <v>174.3</v>
-      </c>
-      <c r="G74" s="1">
-        <v>45155.85</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>10</v>
-      </c>
-      <c r="B75">
-        <v>14</v>
-      </c>
-      <c r="C75">
-        <v>21.513999999999999</v>
-      </c>
-      <c r="D75">
-        <v>0.39900000000000002</v>
-      </c>
-      <c r="E75">
-        <v>0.114</v>
-      </c>
-      <c r="F75">
-        <v>225.3</v>
-      </c>
-      <c r="G75" s="1">
-        <v>60261.94</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>10</v>
-      </c>
-      <c r="B76">
-        <v>15</v>
-      </c>
-      <c r="C76">
-        <v>21.965</v>
-      </c>
-      <c r="D76">
-        <v>0.41499999999999998</v>
-      </c>
-      <c r="E76">
-        <v>0.184</v>
-      </c>
-      <c r="F76">
-        <v>87.6</v>
-      </c>
-      <c r="G76" s="1">
-        <v>38752.36</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>10</v>
-      </c>
-      <c r="B77">
-        <v>16</v>
-      </c>
-      <c r="C77">
-        <v>21.831</v>
-      </c>
-      <c r="D77">
-        <v>0.51400000000000001</v>
-      </c>
-      <c r="E77">
-        <v>0.13800000000000001</v>
-      </c>
-      <c r="F77">
-        <v>275.8</v>
-      </c>
-      <c r="G77" s="1">
-        <v>76670.5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>10</v>
-      </c>
-      <c r="B78">
-        <v>17</v>
-      </c>
-      <c r="C78">
-        <v>22.347000000000001</v>
-      </c>
-      <c r="D78">
-        <v>0.54</v>
-      </c>
-      <c r="E78">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="F78">
-        <v>263.7</v>
-      </c>
-      <c r="G78" s="1">
-        <v>67500.7</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>10</v>
-      </c>
-      <c r="B79">
-        <v>18</v>
-      </c>
-      <c r="C79">
-        <v>22.491</v>
-      </c>
-      <c r="D79">
-        <v>0.51400000000000001</v>
-      </c>
-      <c r="E79">
-        <v>0.161</v>
-      </c>
-      <c r="F79">
-        <v>216.9</v>
-      </c>
-      <c r="G79" s="1">
-        <v>59772.29</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>10</v>
-      </c>
-      <c r="B80">
-        <v>19</v>
-      </c>
-      <c r="C80">
-        <v>22.45</v>
-      </c>
-      <c r="D80">
-        <v>0.496</v>
-      </c>
-      <c r="E80">
-        <v>9.8000000000000004E-2</v>
-      </c>
-      <c r="F80">
-        <v>174.8</v>
-      </c>
-      <c r="G80" s="1">
-        <v>79004.039999999994</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>10</v>
-      </c>
-      <c r="B81">
-        <v>20</v>
-      </c>
-      <c r="C81">
-        <v>22.472000000000001</v>
-      </c>
-      <c r="D81">
-        <v>0.46600000000000003</v>
-      </c>
-      <c r="E81">
-        <v>0.17100000000000001</v>
-      </c>
-      <c r="F81">
-        <v>0.17100000000000001</v>
-      </c>
-      <c r="G81" s="1">
         <v>68964.98</v>
       </c>
     </row>
